--- a/data/trans_orig/IP19C03-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP19C03-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13898</t>
+          <t>13533</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12724</t>
+          <t>12255</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11224</t>
+          <t>10857</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23067</t>
+          <t>22398</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,51%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40897</t>
+          <t>41262</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49692</t>
+          <t>49615</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36634</t>
+          <t>37103</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45241</t>
+          <t>45311</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>81085</t>
+          <t>81754</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>92928</t>
+          <t>93295</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,58%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8943</t>
+          <t>9192</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12314</t>
+          <t>12339</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7470</t>
+          <t>7668</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18090</t>
+          <t>17712</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>22,84%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31555</t>
+          <t>31306</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38404</t>
+          <t>38403</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24732</t>
+          <t>24707</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32966</t>
+          <t>33124</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>59454</t>
+          <t>59832</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>70074</t>
+          <t>69876</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,11%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>3908</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11963</t>
+          <t>11302</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5545</t>
+          <t>5577</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14648</t>
+          <t>14416</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10353</t>
+          <t>11155</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22969</t>
+          <t>22486</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23047</t>
+          <t>23708</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30889</t>
+          <t>31102</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38721</t>
+          <t>38953</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47824</t>
+          <t>47792</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>65410</t>
+          <t>65893</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>78026</t>
+          <t>77224</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>87,38%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13479</t>
+          <t>12865</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25549</t>
+          <t>25544</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11650</t>
+          <t>11259</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23703</t>
+          <t>23207</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27806</t>
+          <t>26752</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45777</t>
+          <t>44613</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>22,96%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72588</t>
+          <t>72593</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>84658</t>
+          <t>85272</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>72451</t>
+          <t>72947</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>84504</t>
+          <t>84895</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>148514</t>
+          <t>149678</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>166485</t>
+          <t>167539</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>86,23%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10962</t>
+          <t>11130</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22138</t>
+          <t>22035</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9196</t>
+          <t>9486</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19840</t>
+          <t>20506</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22867</t>
+          <t>22807</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38365</t>
+          <t>38183</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32520</t>
+          <t>32623</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43696</t>
+          <t>43528</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50195</t>
+          <t>49529</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>60839</t>
+          <t>60549</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>86328</t>
+          <t>86510</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>101826</t>
+          <t>101886</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,71%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6287</t>
+          <t>6832</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15589</t>
+          <t>15553</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>659</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8540</t>
+          <t>8394</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19023</t>
+          <t>18561</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,51%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24411</t>
+          <t>24447</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33713</t>
+          <t>33168</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29174</t>
+          <t>29774</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35058</t>
+          <t>35068</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>56704</t>
+          <t>57166</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>67187</t>
+          <t>67333</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,92%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55508</t>
+          <t>55151</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>78021</t>
+          <t>79388</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47471</t>
+          <t>46922</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>70306</t>
+          <t>69388</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>108134</t>
+          <t>109721</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>139324</t>
+          <t>141389</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>245077</t>
+          <t>243710</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>267590</t>
+          <t>267947</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>271382</t>
+          <t>272300</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>294217</t>
+          <t>294766</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>525462</t>
+          <t>523397</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>556652</t>
+          <t>555065</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,5%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2204</t>
+          <t>1816</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9508</t>
+          <t>9080</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>8844</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>5360</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15462</t>
+          <t>15093</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38730</t>
+          <t>39158</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46034</t>
+          <t>46422</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31721</t>
+          <t>32040</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38899</t>
+          <t>38875</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>73660</t>
+          <t>74029</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83563</t>
+          <t>83762</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6280</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16047</t>
+          <t>15948</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12912</t>
+          <t>12678</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12677</t>
+          <t>12529</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25530</t>
+          <t>25182</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31448</t>
+          <t>31547</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41215</t>
+          <t>41128</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40162</t>
+          <t>40396</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48625</t>
+          <t>48749</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>75039</t>
+          <t>75387</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>87892</t>
+          <t>88040</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,54%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5741</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14928</t>
+          <t>14588</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5912</t>
+          <t>6122</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14756</t>
+          <t>14979</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13679</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25601</t>
+          <t>25033</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>30,71%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26797</t>
+          <t>27137</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35984</t>
+          <t>36307</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25035</t>
+          <t>24812</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33879</t>
+          <t>33669</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>55916</t>
+          <t>56484</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>68425</t>
+          <t>67838</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,22%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16291</t>
+          <t>16030</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29223</t>
+          <t>29669</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14059</t>
+          <t>14477</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26948</t>
+          <t>27399</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33835</t>
+          <t>33750</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51774</t>
+          <t>52652</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,75%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62005</t>
+          <t>61559</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74937</t>
+          <t>75198</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>71590</t>
+          <t>71139</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>84479</t>
+          <t>84061</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>137992</t>
+          <t>137114</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>155931</t>
+          <t>156016</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,21%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14145</t>
+          <t>13513</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26096</t>
+          <t>25649</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13885</t>
+          <t>13886</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26085</t>
+          <t>26778</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30742</t>
+          <t>30740</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48505</t>
+          <t>49204</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,69%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55494</t>
+          <t>55941</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67445</t>
+          <t>68077</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47582</t>
+          <t>46889</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59782</t>
+          <t>59781</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>106753</t>
+          <t>106054</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>124516</t>
+          <t>124518</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>1369</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7376</t>
+          <t>7409</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11394</t>
+          <t>11462</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6315</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16092</t>
+          <t>15643</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18314</t>
+          <t>18281</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23921</t>
+          <t>24321</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26122</t>
+          <t>26054</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34036</t>
+          <t>33928</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>47115</t>
+          <t>47564</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>56563</t>
+          <t>56892</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>90,01%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57214</t>
+          <t>57972</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>82578</t>
+          <t>82771</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>57184</t>
+          <t>57373</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>82313</t>
+          <t>81694</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>122420</t>
+          <t>121408</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>155987</t>
+          <t>155692</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,91%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>253390</t>
+          <t>253197</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>278754</t>
+          <t>277996</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>261158</t>
+          <t>261777</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>286287</t>
+          <t>286098</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>523451</t>
+          <t>523746</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>557018</t>
+          <t>558030</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>82,13%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8544</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15792</t>
+          <t>15483</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20735</t>
+          <t>19918</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34475</t>
+          <t>34656</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41750</t>
+          <t>41684</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34722</t>
+          <t>35031</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44438</t>
+          <t>44177</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>72798</t>
+          <t>73615</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>84470</t>
+          <t>85079</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,96%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>6400</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16375</t>
+          <t>16090</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3550</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12700</t>
+          <t>12730</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12422</t>
+          <t>12392</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25374</t>
+          <t>24308</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39359</t>
+          <t>39644</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49101</t>
+          <t>49334</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>41330</t>
+          <t>41300</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50388</t>
+          <t>50480</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>84390</t>
+          <t>85456</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>97342</t>
+          <t>97372</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,71%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>604</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5427</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1542</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8540</t>
+          <t>7982</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10501</t>
+          <t>10791</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25698</t>
+          <t>25949</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31125</t>
+          <t>30521</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25758</t>
+          <t>26316</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32756</t>
+          <t>32709</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54922</t>
+          <t>54632</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>62649</t>
+          <t>62237</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,13%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12928</t>
+          <t>12884</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26260</t>
+          <t>26568</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13712</t>
+          <t>13880</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27086</t>
+          <t>27687</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29266</t>
+          <t>30137</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48159</t>
+          <t>48335</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84840</t>
+          <t>84532</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98172</t>
+          <t>98216</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77529</t>
+          <t>76928</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>90903</t>
+          <t>90735</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>167556</t>
+          <t>167380</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>186449</t>
+          <t>185578</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,03%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12488</t>
+          <t>12323</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24443</t>
+          <t>23671</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10742</t>
+          <t>10965</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22062</t>
+          <t>22426</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25759</t>
+          <t>25628</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41879</t>
+          <t>41810</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,29%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44720</t>
+          <t>45492</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56675</t>
+          <t>56840</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51523</t>
+          <t>51159</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62843</t>
+          <t>62620</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>100869</t>
+          <t>100938</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>116989</t>
+          <t>117120</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,05%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>4499</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11995</t>
+          <t>12730</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3693</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11906</t>
+          <t>11878</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10245</t>
+          <t>9707</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22199</t>
+          <t>21527</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>33,23%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>19871</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28373</t>
+          <t>28102</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20283</t>
+          <t>20311</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28496</t>
+          <t>28175</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>42591</t>
+          <t>43263</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>54545</t>
+          <t>55083</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>85,02%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49890</t>
+          <t>49603</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>73547</t>
+          <t>72667</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52487</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>76230</t>
+          <t>77573</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>108221</t>
+          <t>108738</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>141763</t>
+          <t>142245</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,56%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>269196</t>
+          <t>270076</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>292853</t>
+          <t>293140</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>273001</t>
+          <t>271658</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>296744</t>
+          <t>297221</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>550211</t>
+          <t>549729</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>583753</t>
+          <t>583236</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,29%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3161</t>
+          <t>3219</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11254</t>
+          <t>12126</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,44 +8653,44 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>4,49%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>16,89%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>8503</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4223</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>14672</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>8,85%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>4,4%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,68%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>8503</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4226</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>14670</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>8,85%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
           <t>15,27%</t>
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>9479</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22834</t>
+          <t>22911</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,65%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60520</t>
+          <t>59648</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68613</t>
+          <t>68555</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,49 +8766,49 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>95,51%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>87587</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>81418</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>91867</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>91,15%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>84,73%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
           <t>95,6%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>87587</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>81420</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>91864</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>91,15%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>84,73%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>95,6%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>199</t>
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>145030</t>
+          <t>144953</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>158636</t>
+          <t>158385</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13685</t>
+          <t>14124</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6204</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17397</t>
+          <t>17874</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13262</t>
+          <t>13019</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27545</t>
+          <t>26867</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,01%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>49016</t>
+          <t>48577</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58267</t>
+          <t>58281</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>54191</t>
+          <t>53714</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65384</t>
+          <t>65301</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>106744</t>
+          <t>107422</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>121027</t>
+          <t>121270</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,31%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3426</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10976</t>
+          <t>11074</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7511</t>
+          <t>7193</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>5739</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16411</t>
+          <t>15153</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>23,61%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16952</t>
+          <t>16854</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24502</t>
+          <t>24694</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28749</t>
+          <t>29067</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34940</t>
+          <t>34920</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>47777</t>
+          <t>49035</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>58728</t>
+          <t>58449</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,06%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17093</t>
+          <t>17244</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32142</t>
+          <t>32130</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23910</t>
+          <t>25206</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44496</t>
+          <t>43976</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46125</t>
+          <t>45916</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70606</t>
+          <t>70768</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,68%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>78905</t>
+          <t>78917</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93954</t>
+          <t>93803</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>82897</t>
+          <t>83417</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>103483</t>
+          <t>102187</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>167833</t>
+          <t>167671</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>192314</t>
+          <t>192523</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,74%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10739</t>
+          <t>10160</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26278</t>
+          <t>25883</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>8913</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24051</t>
+          <t>24444</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21553</t>
+          <t>20962</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45974</t>
+          <t>44718</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,04%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>42220</t>
+          <t>42615</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>57759</t>
+          <t>58338</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>79149</t>
+          <t>78756</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>94711</t>
+          <t>94287</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>125724</t>
+          <t>126980</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>150145</t>
+          <t>150736</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,79%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3607</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11521</t>
+          <t>11659</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9994</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6031</t>
+          <t>6461</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17144</t>
+          <t>18402</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33344</t>
+          <t>33206</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41258</t>
+          <t>41236</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34140</t>
+          <t>34280</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43175</t>
+          <t>42843</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>71855</t>
+          <t>70597</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>82968</t>
+          <t>82538</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>92,74%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55599</t>
+          <t>55259</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>82636</t>
+          <t>82782</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>61648</t>
+          <t>61784</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>92173</t>
+          <t>92942</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>123657</t>
+          <t>124867</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>165513</t>
+          <t>166820</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,27%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>304177</t>
+          <t>304031</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>331214</t>
+          <t>331554</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>386492</t>
+          <t>385723</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>417017</t>
+          <t>416881</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>699965</t>
+          <t>698658</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>741821</t>
+          <t>740611</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,57%</t>
         </is>
       </c>
     </row>
